--- a/employee_surveys/015_employee_benefits_preference_survey--employee_surveys.xlsx
+++ b/employee_surveys/015_employee_benefits_preference_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,201 +515,201 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employee_benefits_preference_survey_form</t>
+          <t>benefits_package_preferred</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Employee Benefits</t>
+          <t>What type of benefits package do you prefer?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>employee_benefits_preference_survey_form_2</t>
+          <t>benefits_options_preferred</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Benefits Preference</t>
+          <t>What benefits options are you interested in?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>benefits_survey_1</t>
+          <t>break_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Benefits Preference</t>
+          <t>How often do you take breaks during the workday?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>benefits_survey_2</t>
+          <t>shift_preference</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Benefits Preference</t>
+          <t>Do you prefer morning, afternoon, or evening work shifts?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>benefits_survey_3</t>
+          <t>work_hours</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Benefits Preference</t>
+          <t>What are your preferred work hours?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>manager_comments</t>
+          <t>work_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manager Comments</t>
+          <t>Do you prefer working from home or in the office?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>manager_comments_2</t>
+          <t>vacation_days</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Manager Comments 2</t>
+          <t>How many vacation days do you prefer?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>date_survey_created</t>
+          <t>health_insurance_preferred</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Date Survey Created</t>
+          <t>What type of health insurance do you prefer?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>time_survey_created</t>
+          <t>health_conditions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Time Survey Created</t>
+          <t>Do you have any health conditions that require special accommodations?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,90 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>date_survey_completed</t>
+          <t>dependents_included</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Date Survey Completed</t>
+          <t>Do you have any family members or dependents that may need to be included in our benefits package?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>time_survey_completed</t>
+          <t>dependents_number</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Time Survey Completed</t>
+          <t>How many dependents do you have that may need benefits?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>employee_benefits_preference_survey_form_3</t>
+          <t>manager_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Employee Benefits</t>
+          <t>Is there anything else you'd like to share about your benefits preferences?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>employee_benefits_preference_survey_form_4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Employee Benefits</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,170 +827,357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>employee_benefits_preference_survey_form_2_choices</t>
+          <t>benefits_package_preferred_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>employee_benefits_preference_survey_form_2_choices</t>
+          <t>benefits_package_preferred_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee_benefits_preference_survey_form_2_choices</t>
+          <t>benefits_package_preferred_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>benefits_survey_1_choices</t>
+          <t>benefits_options_preferred_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>gym_membership</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Gym Membership</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>benefits_survey_1_choices</t>
+          <t>benefits_options_preferred_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>flexible_work_arrangement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Flexible Work Arrangement</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>benefits_survey_1_choices</t>
+          <t>benefits_options_preferred_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>professional_development</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Professional Development</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>benefits_survey_2_choices</t>
+          <t>break_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>benefits_survey_2_choices</t>
+          <t>break_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>benefits_survey_3_choices</t>
+          <t>break_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>benefits_survey_3_choices</t>
+          <t>shift_preference_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>shift_preference_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>afternoon</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>shift_preference_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>work_location_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>work_location_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>health_insurance_preferred_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>traditional</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Traditional</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>health_insurance_preferred_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>health_insurance_preferred_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>health_conditions_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>health_conditions_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dependents_included_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dependents_included_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
